--- a/examples/sport-shop.xlsx
+++ b/examples/sport-shop.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1666800714825-9030be435add?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1666800714825-9030be435add?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1648659487787-79db84e9b2e2?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1648659487787-79db84e9b2e2?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1523362628745-0c100150b504?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1523362628745-0c100150b504?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1516876345887-6dd74f80787a?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1516876345887-6dd74f80787a?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1584827386916-b5351d3ba34b?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1584827386916-b5351d3ba34b?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1653617748437-895c016e88b1?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1653617748437-895c016e88b1?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1662386392771-07d5109da175?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1662386392771-07d5109da175?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1570442387127-66eb80e00938?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1570442387127-66eb80e00938?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1621878974671-86cb5eaed63f?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1621878974671-86cb5eaed63f?w=900&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://images.unsplash.com/photo-1728034262220-91bdcea31c3a?w=800&amp;q=75&amp;auto=format&amp;fit=crop</t>
+          <t>https://images.unsplash.com/photo-1728034262220-91bdcea31c3a?w=1800&amp;h=1200&amp;fit=crop&amp;crop=entropy&amp;q=75&amp;auto=format</t>
         </is>
       </c>
     </row>
